--- a/Experiment_3/results/Experiment_3_results.xlsx
+++ b/Experiment_3/results/Experiment_3_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="53">
   <si>
     <t>VITEK</t>
   </si>
@@ -145,16 +145,31 @@
     <t>Internal</t>
   </si>
   <si>
-    <t>Min 20 R Sens</t>
+    <t>Antimicrobial Agent</t>
   </si>
   <si>
-    <t>Min 200 samples VITEK</t>
+    <t>S</t>
   </si>
   <si>
-    <t>Trim Sulf</t>
+    <t>R</t>
   </si>
   <si>
-    <t>Amp Sul</t>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Vitek count</t>
+  </si>
+  <si>
+    <t>Amoxicillin-clavulanic acid</t>
+  </si>
+  <si>
+    <t>Ampicillin</t>
+  </si>
+  <si>
+    <t>Ceftriaxone</t>
+  </si>
+  <si>
+    <t>Sensititre count</t>
   </si>
 </sst>
 </file>
@@ -232,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -260,11 +275,14 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <font/>
       <fill>
@@ -291,6 +309,28 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFD966"/>
           <bgColor rgb="FFFFD966"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
       <border/>
@@ -447,11 +487,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="15264153"/>
-        <c:axId val="1443732890"/>
+        <c:axId val="1383927011"/>
+        <c:axId val="2048478021"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="15264153"/>
+        <c:axId val="1383927011"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -507,10 +547,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1443732890"/>
+        <c:crossAx val="2048478021"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1443732890"/>
+        <c:axId val="2048478021"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0.5"/>
@@ -588,7 +628,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15264153"/>
+        <c:crossAx val="1383927011"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -618,10 +658,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>790575</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4705350" cy="3533775"/>
     <xdr:graphicFrame>
@@ -5207,7 +5247,7 @@
         <v>3.431372549</v>
       </c>
       <c r="O99" s="10">
-        <f t="shared" ref="O99:T99" si="19">MEDIAN(O96:O98)</f>
+        <f t="shared" ref="O99:V99" si="19">MEDIAN(O96:O98)</f>
         <v>0.08683657669</v>
       </c>
       <c r="P99" s="10">
@@ -5230,6 +5270,14 @@
         <f t="shared" si="19"/>
         <v>0.087865957</v>
       </c>
+      <c r="U99" s="10">
+        <f t="shared" si="19"/>
+        <v>3.679192892</v>
+      </c>
+      <c r="V99" s="10">
+        <f t="shared" si="19"/>
+        <v>4.012427829</v>
+      </c>
     </row>
     <row r="101">
       <c r="B101" s="1" t="s">
@@ -5536,7 +5584,7 @@
         <v>44.60784314</v>
       </c>
       <c r="O106" s="10">
-        <f t="shared" ref="O106:T106" si="21">MEDIAN(O103:O105)</f>
+        <f t="shared" ref="O106:V106" si="21">MEDIAN(O103:O105)</f>
         <v>0.01534086586</v>
       </c>
       <c r="P106" s="10">
@@ -5559,6 +5607,14 @@
         <f t="shared" si="21"/>
         <v>0.01513465245</v>
       </c>
+      <c r="U106" s="10">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="V106" s="10">
+        <f t="shared" si="21"/>
+        <v>0.8490445135</v>
+      </c>
     </row>
     <row r="108">
       <c r="B108" s="1" t="s">
@@ -5865,7 +5921,7 @@
         <v>29.73856209</v>
       </c>
       <c r="O113" s="10">
-        <f t="shared" ref="O113:T113" si="23">MEDIAN(O110:O112)</f>
+        <f t="shared" ref="O113:V113" si="23">MEDIAN(O110:O112)</f>
         <v>0.0795803638</v>
       </c>
       <c r="P113" s="10">
@@ -5887,6 +5943,14 @@
       <c r="T113" s="10">
         <f t="shared" si="23"/>
         <v>0.07533921027</v>
+      </c>
+      <c r="U113" s="10">
+        <f t="shared" si="23"/>
+        <v>1.222763852</v>
+      </c>
+      <c r="V113" s="10">
+        <f t="shared" si="23"/>
+        <v>9.038769076</v>
       </c>
     </row>
     <row r="116">
@@ -6008,21 +6072,199 @@
       </c>
     </row>
     <row r="122">
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="4"/>
+      <c r="D122" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H122" s="4"/>
+      <c r="I122" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J122" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="C123" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D123" s="11">
+        <f>J106</f>
+        <v>44.60784314</v>
+      </c>
+      <c r="E123" s="11">
+        <f>I106</f>
+        <v>0</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I123" s="11">
+        <f>V106</f>
+        <v>0.8490445135</v>
+      </c>
+      <c r="J123" s="11">
+        <f>U106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="C124" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D124" s="11">
+        <f>J113</f>
+        <v>29.73856209</v>
+      </c>
+      <c r="E124" s="11">
+        <f>I113</f>
+        <v>1.960784314</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I124" s="11">
+        <f>V113</f>
+        <v>9.038769076</v>
+      </c>
+      <c r="J124" s="11">
+        <f>U113</f>
+        <v>1.222763852</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="C125" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D125" s="11">
+        <f>J99</f>
+        <v>3.431372549</v>
+      </c>
+      <c r="E125" s="11">
+        <f>I99</f>
+        <v>10.29411765</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I125" s="11">
+        <f>V99</f>
+        <v>4.012427829</v>
+      </c>
+      <c r="J125" s="11">
+        <f>U99</f>
+        <v>3.679192892</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="H127" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="I127" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="123">
-      <c r="C123" s="1" t="s">
+      <c r="J127" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="124">
-      <c r="C124" s="1" t="s">
+      <c r="K127" s="3" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="H128" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="H129" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I129" s="7">
+        <v>839.0</v>
+      </c>
+      <c r="J129" s="7">
+        <v>295.0</v>
+      </c>
+      <c r="K129" s="7">
+        <v>1134.0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="H130" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I130" s="7">
+        <v>32.0</v>
+      </c>
+      <c r="J130" s="7">
+        <v>199.0</v>
+      </c>
+      <c r="K130" s="7">
+        <v>231.0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="H131" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I131" s="7">
+        <v>83.0</v>
+      </c>
+      <c r="J131" s="7">
+        <v>136.0</v>
+      </c>
+      <c r="K131" s="7">
+        <v>219.0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="H132" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="H133" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I133" s="7">
+        <v>69.0</v>
+      </c>
+      <c r="J133" s="7">
+        <v>49.0</v>
+      </c>
+      <c r="K133" s="7">
+        <v>118.0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="H134" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I134" s="7">
+        <v>91.0</v>
+      </c>
+      <c r="J134" s="7">
+        <v>115.0</v>
+      </c>
+      <c r="K134" s="7">
+        <v>206.0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="H135" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I135" s="7">
+        <v>164.0</v>
+      </c>
+      <c r="J135" s="7">
+        <v>42.0</v>
+      </c>
+      <c r="K135" s="7">
+        <v>206.0</v>
       </c>
     </row>
   </sheetData>
@@ -6054,6 +6296,16 @@
       <formula>0.85</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="M3:N8">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M12:N17">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+      <formula>10</formula>
+    </cfRule>
+  </conditionalFormatting>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>